--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122657569</v>
       </c>
       <c r="B2" t="n">
-        <v>57333</v>
+        <v>57334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,1014 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122883139</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>626440</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6706532</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122883200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>626442</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706553</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122883171</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626428</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706556</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122883333</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626446</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706557</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122882687</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90909</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626434</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706472</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122882622</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706558</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122883128</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626429</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706541</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122883148</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626438</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706552</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122883446</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626445</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706555</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883139</v>
+        <v>122883148</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626440</v>
+        <v>626438</v>
       </c>
       <c r="R3" t="n">
-        <v>6706532</v>
+        <v>6706552</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883200</v>
+        <v>122883446</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626442</v>
+        <v>626445</v>
       </c>
       <c r="R4" t="n">
-        <v>6706553</v>
+        <v>6706555</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883171</v>
+        <v>122883200</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626428</v>
+        <v>626442</v>
       </c>
       <c r="R5" t="n">
-        <v>6706556</v>
+        <v>6706553</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883333</v>
+        <v>122883171</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626446</v>
+        <v>626428</v>
       </c>
       <c r="R6" t="n">
-        <v>6706557</v>
+        <v>6706556</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122882687</v>
+        <v>122883333</v>
       </c>
       <c r="B7" t="n">
-        <v>90909</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,25 +1259,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626434</v>
+        <v>626446</v>
       </c>
       <c r="R7" t="n">
-        <v>6706472</v>
+        <v>6706557</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122882622</v>
+        <v>122883139</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626445</v>
+        <v>626440</v>
       </c>
       <c r="R8" t="n">
-        <v>6706558</v>
+        <v>6706532</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883128</v>
+        <v>122882687</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,25 +1483,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626429</v>
+        <v>626434</v>
       </c>
       <c r="R9" t="n">
-        <v>6706541</v>
+        <v>6706472</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,7 +1583,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122883148</v>
+        <v>122882622</v>
       </c>
       <c r="B10" t="n">
         <v>98355</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626438</v>
+        <v>626445</v>
       </c>
       <c r="R10" t="n">
-        <v>6706552</v>
+        <v>6706558</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883446</v>
+        <v>122883128</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626445</v>
+        <v>626429</v>
       </c>
       <c r="R11" t="n">
-        <v>6706555</v>
+        <v>6706541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883148</v>
+        <v>122882687</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626438</v>
+        <v>626434</v>
       </c>
       <c r="R3" t="n">
-        <v>6706552</v>
+        <v>6706472</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883446</v>
+        <v>122883200</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626445</v>
+        <v>626442</v>
       </c>
       <c r="R4" t="n">
-        <v>6706555</v>
+        <v>6706553</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883200</v>
+        <v>122883446</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626442</v>
+        <v>626445</v>
       </c>
       <c r="R5" t="n">
-        <v>6706553</v>
+        <v>6706555</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883171</v>
+        <v>122883148</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626428</v>
+        <v>626438</v>
       </c>
       <c r="R6" t="n">
-        <v>6706556</v>
+        <v>6706552</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883333</v>
+        <v>122883171</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626446</v>
+        <v>626428</v>
       </c>
       <c r="R7" t="n">
-        <v>6706557</v>
+        <v>6706556</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
         <v>122883139</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122882687</v>
+        <v>122883333</v>
       </c>
       <c r="B9" t="n">
-        <v>90909</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,25 +1483,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626434</v>
+        <v>626446</v>
       </c>
       <c r="R9" t="n">
-        <v>6706472</v>
+        <v>6706557</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
         <v>122882622</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>122883128</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122882687</v>
+        <v>122883200</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626434</v>
+        <v>626442</v>
       </c>
       <c r="R3" t="n">
-        <v>6706472</v>
+        <v>6706553</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883200</v>
+        <v>122883148</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626442</v>
+        <v>626438</v>
       </c>
       <c r="R4" t="n">
-        <v>6706553</v>
+        <v>6706552</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883148</v>
+        <v>122882687</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>90909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626438</v>
+        <v>626434</v>
       </c>
       <c r="R6" t="n">
-        <v>6706552</v>
+        <v>6706472</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883171</v>
+        <v>122883128</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626428</v>
+        <v>626429</v>
       </c>
       <c r="R7" t="n">
-        <v>6706556</v>
+        <v>6706541</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883139</v>
+        <v>122883171</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626440</v>
+        <v>626428</v>
       </c>
       <c r="R8" t="n">
-        <v>6706532</v>
+        <v>6706556</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883128</v>
+        <v>122883139</v>
       </c>
       <c r="B11" t="n">
         <v>98357</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626429</v>
+        <v>626440</v>
       </c>
       <c r="R11" t="n">
-        <v>6706541</v>
+        <v>6706532</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883200</v>
+        <v>122883128</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626442</v>
+        <v>626429</v>
       </c>
       <c r="R3" t="n">
-        <v>6706553</v>
+        <v>6706541</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883148</v>
+        <v>122883200</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626438</v>
+        <v>626442</v>
       </c>
       <c r="R4" t="n">
-        <v>6706552</v>
+        <v>6706553</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883446</v>
+        <v>122883139</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626445</v>
+        <v>626440</v>
       </c>
       <c r="R5" t="n">
-        <v>6706555</v>
+        <v>6706532</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122882687</v>
+        <v>122883333</v>
       </c>
       <c r="B6" t="n">
-        <v>90909</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626434</v>
+        <v>626446</v>
       </c>
       <c r="R6" t="n">
-        <v>6706472</v>
+        <v>6706557</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883128</v>
+        <v>122883148</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626429</v>
+        <v>626438</v>
       </c>
       <c r="R7" t="n">
-        <v>6706541</v>
+        <v>6706552</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883171</v>
+        <v>122882687</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>90917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626428</v>
+        <v>626434</v>
       </c>
       <c r="R8" t="n">
-        <v>6706556</v>
+        <v>6706472</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883333</v>
+        <v>122883171</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626446</v>
+        <v>626428</v>
       </c>
       <c r="R9" t="n">
-        <v>6706557</v>
+        <v>6706556</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
         <v>122882622</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883139</v>
+        <v>122883446</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626440</v>
+        <v>626445</v>
       </c>
       <c r="R11" t="n">
-        <v>6706532</v>
+        <v>6706555</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883128</v>
+        <v>122883171</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626429</v>
+        <v>626428</v>
       </c>
       <c r="R3" t="n">
-        <v>6706541</v>
+        <v>6706556</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883200</v>
+        <v>122883333</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626442</v>
+        <v>626446</v>
       </c>
       <c r="R4" t="n">
-        <v>6706553</v>
+        <v>6706557</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883139</v>
+        <v>122883200</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626440</v>
+        <v>626442</v>
       </c>
       <c r="R5" t="n">
-        <v>6706532</v>
+        <v>6706553</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883333</v>
+        <v>122882622</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626446</v>
+        <v>626445</v>
       </c>
       <c r="R6" t="n">
-        <v>6706557</v>
+        <v>6706558</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883148</v>
+        <v>122883139</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626438</v>
+        <v>626440</v>
       </c>
       <c r="R7" t="n">
-        <v>6706552</v>
+        <v>6706532</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122882687</v>
+        <v>122883148</v>
       </c>
       <c r="B8" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626434</v>
+        <v>626438</v>
       </c>
       <c r="R8" t="n">
-        <v>6706472</v>
+        <v>6706552</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883171</v>
+        <v>122883446</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626428</v>
+        <v>626445</v>
       </c>
       <c r="R9" t="n">
-        <v>6706556</v>
+        <v>6706555</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882622</v>
+        <v>122882687</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626445</v>
+        <v>626434</v>
       </c>
       <c r="R10" t="n">
-        <v>6706558</v>
+        <v>6706472</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883446</v>
+        <v>122883128</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626445</v>
+        <v>626429</v>
       </c>
       <c r="R11" t="n">
-        <v>6706555</v>
+        <v>6706541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882687</v>
+        <v>122883128</v>
       </c>
       <c r="B10" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626434</v>
+        <v>626429</v>
       </c>
       <c r="R10" t="n">
-        <v>6706472</v>
+        <v>6706541</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883128</v>
+        <v>122882687</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626429</v>
+        <v>626434</v>
       </c>
       <c r="R11" t="n">
-        <v>6706541</v>
+        <v>6706472</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883171</v>
+        <v>122883200</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626428</v>
+        <v>626442</v>
       </c>
       <c r="R3" t="n">
-        <v>6706556</v>
+        <v>6706553</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883333</v>
+        <v>122883171</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626446</v>
+        <v>626428</v>
       </c>
       <c r="R4" t="n">
-        <v>6706557</v>
+        <v>6706556</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883200</v>
+        <v>122883333</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626442</v>
+        <v>626446</v>
       </c>
       <c r="R5" t="n">
-        <v>6706553</v>
+        <v>6706557</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122882622</v>
+        <v>122883139</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626445</v>
+        <v>626440</v>
       </c>
       <c r="R6" t="n">
-        <v>6706558</v>
+        <v>6706532</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883139</v>
+        <v>122883148</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626440</v>
+        <v>626438</v>
       </c>
       <c r="R7" t="n">
-        <v>6706532</v>
+        <v>6706552</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883148</v>
+        <v>122882622</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626438</v>
+        <v>626445</v>
       </c>
       <c r="R8" t="n">
-        <v>6706552</v>
+        <v>6706558</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883446</v>
+        <v>122883128</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626445</v>
+        <v>626429</v>
       </c>
       <c r="R9" t="n">
-        <v>6706555</v>
+        <v>6706541</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,7 +1583,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122883128</v>
+        <v>122883446</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626429</v>
+        <v>626445</v>
       </c>
       <c r="R10" t="n">
-        <v>6706541</v>
+        <v>6706555</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883200</v>
+        <v>122882622</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626442</v>
+        <v>626445</v>
       </c>
       <c r="R3" t="n">
-        <v>6706553</v>
+        <v>6706558</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883171</v>
+        <v>122883218</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626428</v>
+        <v>626442</v>
       </c>
       <c r="R4" t="n">
-        <v>6706556</v>
+        <v>6706553</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883148</v>
+        <v>122883171</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626438</v>
+        <v>626428</v>
       </c>
       <c r="R7" t="n">
-        <v>6706552</v>
+        <v>6706556</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122882622</v>
+        <v>122883148</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626445</v>
+        <v>626438</v>
       </c>
       <c r="R8" t="n">
-        <v>6706558</v>
+        <v>6706552</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122883446</v>
+        <v>122882687</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626445</v>
+        <v>626434</v>
       </c>
       <c r="R10" t="n">
-        <v>6706555</v>
+        <v>6706472</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122882687</v>
+        <v>122883446</v>
       </c>
       <c r="B11" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626434</v>
+        <v>626445</v>
       </c>
       <c r="R11" t="n">
-        <v>6706472</v>
+        <v>6706555</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122882622</v>
+        <v>122883200</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626445</v>
+        <v>626442</v>
       </c>
       <c r="R3" t="n">
-        <v>6706558</v>
+        <v>6706553</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883218</v>
+        <v>122883446</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626442</v>
+        <v>626445</v>
       </c>
       <c r="R4" t="n">
-        <v>6706553</v>
+        <v>6706555</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883333</v>
+        <v>122883171</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626446</v>
+        <v>626428</v>
       </c>
       <c r="R5" t="n">
-        <v>6706557</v>
+        <v>6706556</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883139</v>
+        <v>122882687</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>90920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626440</v>
+        <v>626434</v>
       </c>
       <c r="R6" t="n">
-        <v>6706532</v>
+        <v>6706472</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883171</v>
+        <v>122883333</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626428</v>
+        <v>626446</v>
       </c>
       <c r="R7" t="n">
-        <v>6706556</v>
+        <v>6706557</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883148</v>
+        <v>122883128</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626438</v>
+        <v>626429</v>
       </c>
       <c r="R8" t="n">
-        <v>6706552</v>
+        <v>6706541</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883128</v>
+        <v>122883148</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626429</v>
+        <v>626438</v>
       </c>
       <c r="R9" t="n">
-        <v>6706541</v>
+        <v>6706552</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882687</v>
+        <v>122882622</v>
       </c>
       <c r="B10" t="n">
-        <v>90917</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626434</v>
+        <v>626445</v>
       </c>
       <c r="R10" t="n">
-        <v>6706472</v>
+        <v>6706558</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883446</v>
+        <v>122883139</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626445</v>
+        <v>626440</v>
       </c>
       <c r="R11" t="n">
-        <v>6706555</v>
+        <v>6706532</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883200</v>
+        <v>122883218</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>122883446</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>122883171</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122882687</v>
+        <v>122883148</v>
       </c>
       <c r="B6" t="n">
-        <v>90920</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626434</v>
+        <v>626438</v>
       </c>
       <c r="R6" t="n">
-        <v>6706472</v>
+        <v>6706552</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883333</v>
+        <v>122883128</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626446</v>
+        <v>626429</v>
       </c>
       <c r="R7" t="n">
-        <v>6706557</v>
+        <v>6706541</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883128</v>
+        <v>122882622</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626429</v>
+        <v>626445</v>
       </c>
       <c r="R8" t="n">
-        <v>6706541</v>
+        <v>6706558</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883148</v>
+        <v>122882687</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>90922</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,25 +1483,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626438</v>
+        <v>626434</v>
       </c>
       <c r="R9" t="n">
-        <v>6706552</v>
+        <v>6706472</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882622</v>
+        <v>122883333</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626445</v>
+        <v>626446</v>
       </c>
       <c r="R10" t="n">
-        <v>6706558</v>
+        <v>6706557</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,7 +1698,7 @@
         <v>122883139</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883218</v>
+        <v>122883139</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626442</v>
+        <v>626440</v>
       </c>
       <c r="R3" t="n">
-        <v>6706553</v>
+        <v>6706532</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883446</v>
+        <v>122883333</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626445</v>
+        <v>626446</v>
       </c>
       <c r="R4" t="n">
-        <v>6706555</v>
+        <v>6706557</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883171</v>
+        <v>122883128</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626428</v>
+        <v>626429</v>
       </c>
       <c r="R5" t="n">
-        <v>6706556</v>
+        <v>6706541</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883148</v>
+        <v>122883171</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626438</v>
+        <v>626428</v>
       </c>
       <c r="R6" t="n">
-        <v>6706552</v>
+        <v>6706556</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883128</v>
+        <v>122883148</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626429</v>
+        <v>626438</v>
       </c>
       <c r="R7" t="n">
-        <v>6706541</v>
+        <v>6706552</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,7 +1362,7 @@
         <v>122882622</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>122882687</v>
       </c>
       <c r="B9" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122883333</v>
+        <v>122883218</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626446</v>
+        <v>626442</v>
       </c>
       <c r="R10" t="n">
-        <v>6706557</v>
+        <v>6706553</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122883139</v>
+        <v>122883446</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626440</v>
+        <v>626445</v>
       </c>
       <c r="R11" t="n">
-        <v>6706532</v>
+        <v>6706555</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55547-2024 artfynd.xlsx
+++ b/artfynd/A 55547-2024 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122882687</v>
+        <v>122883148</v>
       </c>
       <c r="B8" t="n">
-        <v>90931</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626434</v>
+        <v>626438</v>
       </c>
       <c r="R8" t="n">
-        <v>6706472</v>
+        <v>6706552</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122883148</v>
+        <v>122882687</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>90931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,25 +1483,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626438</v>
+        <v>626434</v>
       </c>
       <c r="R9" t="n">
-        <v>6706552</v>
+        <v>6706472</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
